--- a/ConfigExcels/ShopItem.xlsx
+++ b/ConfigExcels/ShopItem.xlsx
@@ -73,12 +73,10 @@
     <font>
       <b/>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
     <font>
@@ -767,7 +765,366 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1"/>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="5">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3001</v>
+      </c>
+      <c r="C6" s="7">
+        <v>100</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="6">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7">
+        <v>3002</v>
+      </c>
+      <c r="C7" s="7">
+        <v>200</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="5">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7">
+        <v>3003</v>
+      </c>
+      <c r="C8" s="7">
+        <v>400</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="6">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>3004</v>
+      </c>
+      <c r="C9" s="7">
+        <v>100</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="5">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7">
+        <v>3005</v>
+      </c>
+      <c r="C10" s="7">
+        <v>200</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="6">
+        <v>2</v>
+      </c>
+      <c r="B11" s="7">
+        <v>3006</v>
+      </c>
+      <c r="C11" s="7">
+        <v>400</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="5">
+        <v>2</v>
+      </c>
+      <c r="B12" s="7">
+        <v>3007</v>
+      </c>
+      <c r="C12" s="7">
+        <v>100</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="6">
+        <v>2</v>
+      </c>
+      <c r="B13" s="7">
+        <v>3008</v>
+      </c>
+      <c r="C13" s="7">
+        <v>200</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="5">
+        <v>2</v>
+      </c>
+      <c r="B14" s="7">
+        <v>3009</v>
+      </c>
+      <c r="C14" s="7">
+        <v>400</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="6">
+        <v>2</v>
+      </c>
+      <c r="B15" s="7">
+        <v>3010</v>
+      </c>
+      <c r="C15" s="7">
+        <v>100</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="5">
+        <v>2</v>
+      </c>
+      <c r="B16" s="7">
+        <v>3011</v>
+      </c>
+      <c r="C16" s="7">
+        <v>200</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="6">
+        <v>2</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3012</v>
+      </c>
+      <c r="C17" s="7">
+        <v>400</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="5">
+        <v>2</v>
+      </c>
+      <c r="B18" s="7">
+        <v>3013</v>
+      </c>
+      <c r="C18" s="7">
+        <v>100</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="6">
+        <v>2</v>
+      </c>
+      <c r="B19" s="7">
+        <v>3014</v>
+      </c>
+      <c r="C19" s="7">
+        <v>200</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="5">
+        <v>2</v>
+      </c>
+      <c r="B20" s="7">
+        <v>3015</v>
+      </c>
+      <c r="C20" s="7">
+        <v>400</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="6">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>3016</v>
+      </c>
+      <c r="C21" s="7">
+        <v>100</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="5">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7">
+        <v>3017</v>
+      </c>
+      <c r="C22" s="7">
+        <v>200</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1</v>
+      </c>
+      <c r="F22" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="6">
+        <v>2</v>
+      </c>
+      <c r="B23" s="7">
+        <v>3018</v>
+      </c>
+      <c r="C23" s="7">
+        <v>400</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
